--- a/project/outputs_xlsx_solution/test33.4-wide-NR-4.xlsx
+++ b/project/outputs_xlsx_solution/test33.4-wide-NR-4.xlsx
@@ -1005,15 +1005,6 @@
       <c r="EO1">
         <v>142</v>
       </c>
-      <c r="EP1">
-        <v>143</v>
-      </c>
-      <c r="EQ1">
-        <v>144</v>
-      </c>
-      <c r="ER1">
-        <v>145</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -1715,12 +1706,9 @@
         <v>33</v>
       </c>
       <c r="AB24" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="AC24" t="s">
-        <v>14</v>
-      </c>
-      <c r="AD24" t="s">
         <v>21</v>
       </c>
       <c r="AF24" t="s">
@@ -1737,11 +1725,14 @@
       <c r="C25" t="s">
         <v>27</v>
       </c>
+      <c r="AC25" t="s">
+        <v>5</v>
+      </c>
       <c r="AD25" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AE25" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AF25" t="s">
         <v>14</v>
@@ -1760,11 +1751,14 @@
       <c r="C26" t="s">
         <v>28</v>
       </c>
+      <c r="AC26" t="s">
+        <v>5</v>
+      </c>
       <c r="AD26" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AE26" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="AF26" t="s">
         <v>34</v>
@@ -1795,10 +1789,10 @@
       <c r="C27" t="s">
         <v>29</v>
       </c>
+      <c r="AC27" t="s">
+        <v>5</v>
+      </c>
       <c r="AD27" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE27" t="s">
         <v>9</v>
       </c>
       <c r="AF27" t="s">
@@ -1827,10 +1821,10 @@
       <c r="C28" t="s">
         <v>30</v>
       </c>
+      <c r="AC28" t="s">
+        <v>5</v>
+      </c>
       <c r="AD28" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE28" t="s">
         <v>9</v>
       </c>
       <c r="AF28" t="s">
@@ -1853,11 +1847,14 @@
       <c r="C29" t="s">
         <v>31</v>
       </c>
+      <c r="AD29" t="s">
+        <v>5</v>
+      </c>
       <c r="AE29" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AF29" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="AG29" t="s">
         <v>14</v>
@@ -1879,10 +1876,10 @@
       <c r="C30" t="s">
         <v>32</v>
       </c>
+      <c r="AD30" t="s">
+        <v>5</v>
+      </c>
       <c r="AE30" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF30" t="s">
         <v>9</v>
       </c>
       <c r="AG30" t="s">
@@ -1898,12 +1895,9 @@
         <v>33</v>
       </c>
       <c r="AK30" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="AL30" t="s">
-        <v>14</v>
-      </c>
-      <c r="AM30" t="s">
         <v>21</v>
       </c>
       <c r="AO30" t="s">
@@ -1920,10 +1914,10 @@
       <c r="C31" t="s">
         <v>27</v>
       </c>
+      <c r="AE31" t="s">
+        <v>5</v>
+      </c>
       <c r="AF31" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG31" t="s">
         <v>9</v>
       </c>
       <c r="AK31" t="s">
@@ -1955,10 +1949,10 @@
       <c r="C32" t="s">
         <v>28</v>
       </c>
+      <c r="AE32" t="s">
+        <v>5</v>
+      </c>
       <c r="AF32" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG32" t="s">
         <v>9</v>
       </c>
       <c r="AN32" t="s">
@@ -1993,10 +1987,10 @@
       <c r="C33" t="s">
         <v>29</v>
       </c>
+      <c r="AE33" t="s">
+        <v>5</v>
+      </c>
       <c r="AF33" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG33" t="s">
         <v>9</v>
       </c>
       <c r="AO33" t="s">
@@ -2025,10 +2019,10 @@
       <c r="C34" t="s">
         <v>30</v>
       </c>
+      <c r="AE34" t="s">
+        <v>5</v>
+      </c>
       <c r="AF34" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG34" t="s">
         <v>9</v>
       </c>
       <c r="AO34" t="s">
@@ -2051,10 +2045,10 @@
       <c r="C35" t="s">
         <v>31</v>
       </c>
+      <c r="AF35" t="s">
+        <v>5</v>
+      </c>
       <c r="AG35" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH35" t="s">
         <v>9</v>
       </c>
       <c r="AO35" t="s">
@@ -2080,10 +2074,10 @@
       <c r="C36" t="s">
         <v>32</v>
       </c>
+      <c r="AF36" t="s">
+        <v>5</v>
+      </c>
       <c r="AG36" t="s">
-        <v>5</v>
-      </c>
-      <c r="AH36" t="s">
         <v>9</v>
       </c>
       <c r="AP36" t="s">
@@ -2099,12 +2093,9 @@
         <v>33</v>
       </c>
       <c r="AT36" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="AU36" t="s">
-        <v>14</v>
-      </c>
-      <c r="AV36" t="s">
         <v>21</v>
       </c>
       <c r="AX36" t="s">
@@ -2121,11 +2112,14 @@
       <c r="C37" t="s">
         <v>35</v>
       </c>
+      <c r="AU37" t="s">
+        <v>5</v>
+      </c>
       <c r="AV37" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AW37" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AX37" t="s">
         <v>14</v>
@@ -2134,9 +2128,6 @@
         <v>14</v>
       </c>
       <c r="AZ37" t="s">
-        <v>14</v>
-      </c>
-      <c r="BA37" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2150,15 +2141,21 @@
       <c r="C38" t="s">
         <v>36</v>
       </c>
+      <c r="AU38" t="s">
+        <v>5</v>
+      </c>
       <c r="AV38" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AW38" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="AX38" t="s">
         <v>34</v>
       </c>
+      <c r="AZ38" t="s">
+        <v>14</v>
+      </c>
       <c r="BA38" t="s">
         <v>14</v>
       </c>
@@ -2166,9 +2163,6 @@
         <v>14</v>
       </c>
       <c r="BC38" t="s">
-        <v>14</v>
-      </c>
-      <c r="BD38" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2182,10 +2176,10 @@
       <c r="C39" t="s">
         <v>37</v>
       </c>
+      <c r="AU39" t="s">
+        <v>5</v>
+      </c>
       <c r="AV39" t="s">
-        <v>5</v>
-      </c>
-      <c r="AW39" t="s">
         <v>9</v>
       </c>
       <c r="AX39" t="s">
@@ -2194,7 +2188,7 @@
       <c r="AY39" t="s">
         <v>21</v>
       </c>
-      <c r="BD39" t="s">
+      <c r="BC39" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2208,7 +2202,7 @@
       <c r="C40" t="s">
         <v>38</v>
       </c>
-      <c r="AV40" t="s">
+      <c r="AU40" t="s">
         <v>5</v>
       </c>
       <c r="AX40" t="s">
@@ -2217,7 +2211,7 @@
       <c r="AY40" t="s">
         <v>21</v>
       </c>
-      <c r="BD40" t="s">
+      <c r="BC40" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2231,20 +2225,23 @@
       <c r="C41" t="s">
         <v>18</v>
       </c>
+      <c r="AV41" t="s">
+        <v>5</v>
+      </c>
       <c r="AW41" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AX41" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="AY41" t="s">
         <v>33</v>
       </c>
       <c r="AZ41" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="BA41" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BB41" t="s">
         <v>14</v>
@@ -2253,9 +2250,6 @@
         <v>14</v>
       </c>
       <c r="BD41" t="s">
-        <v>14</v>
-      </c>
-      <c r="BE41" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2269,11 +2263,14 @@
       <c r="C42" t="s">
         <v>19</v>
       </c>
+      <c r="AV42" t="s">
+        <v>5</v>
+      </c>
       <c r="AW42" t="s">
-        <v>5</v>
-      </c>
-      <c r="AX42" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="AZ42" t="s">
+        <v>33</v>
       </c>
       <c r="BA42" t="s">
         <v>33</v>
@@ -2282,10 +2279,10 @@
         <v>33</v>
       </c>
       <c r="BC42" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="BD42" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="BE42" t="s">
         <v>14</v>
@@ -2294,9 +2291,6 @@
         <v>14</v>
       </c>
       <c r="BG42" t="s">
-        <v>14</v>
-      </c>
-      <c r="BH42" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2310,15 +2304,18 @@
       <c r="C43" t="s">
         <v>20</v>
       </c>
+      <c r="AV43" t="s">
+        <v>5</v>
+      </c>
       <c r="AW43" t="s">
-        <v>5</v>
-      </c>
-      <c r="AX43" t="s">
-        <v>9</v>
-      </c>
-      <c r="BD43" t="s">
+        <v>9</v>
+      </c>
+      <c r="BC43" t="s">
         <v>34</v>
       </c>
+      <c r="BG43" t="s">
+        <v>14</v>
+      </c>
       <c r="BH43" t="s">
         <v>14</v>
       </c>
@@ -2329,9 +2326,6 @@
         <v>14</v>
       </c>
       <c r="BK43" t="s">
-        <v>14</v>
-      </c>
-      <c r="BL43" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2345,11 +2339,14 @@
       <c r="C44" t="s">
         <v>23</v>
       </c>
+      <c r="AV44" t="s">
+        <v>5</v>
+      </c>
       <c r="AW44" t="s">
-        <v>5</v>
-      </c>
-      <c r="AX44" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="BC44" t="s">
+        <v>14</v>
       </c>
       <c r="BD44" t="s">
         <v>14</v>
@@ -2361,12 +2358,9 @@
         <v>14</v>
       </c>
       <c r="BG44" t="s">
-        <v>14</v>
-      </c>
-      <c r="BH44" t="s">
         <v>21</v>
       </c>
-      <c r="BL44" t="s">
+      <c r="BK44" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2380,14 +2374,17 @@
       <c r="C45" t="s">
         <v>24</v>
       </c>
+      <c r="AW45" t="s">
+        <v>5</v>
+      </c>
       <c r="AX45" t="s">
-        <v>5</v>
-      </c>
-      <c r="AY45" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="BC45" t="s">
+        <v>33</v>
       </c>
       <c r="BD45" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="BE45" t="s">
         <v>14</v>
@@ -2405,12 +2402,9 @@
         <v>14</v>
       </c>
       <c r="BJ45" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="BK45" t="s">
-        <v>21</v>
-      </c>
-      <c r="BL45" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2424,11 +2418,14 @@
       <c r="C46" t="s">
         <v>25</v>
       </c>
+      <c r="AW46" t="s">
+        <v>5</v>
+      </c>
       <c r="AX46" t="s">
-        <v>5</v>
-      </c>
-      <c r="AY46" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="BD46" t="s">
+        <v>33</v>
       </c>
       <c r="BE46" t="s">
         <v>33</v>
@@ -2437,15 +2434,12 @@
         <v>33</v>
       </c>
       <c r="BG46" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="BH46" t="s">
-        <v>14</v>
-      </c>
-      <c r="BI46" t="s">
         <v>21</v>
       </c>
-      <c r="BL46" t="s">
+      <c r="BK46" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2459,11 +2453,14 @@
       <c r="C47" t="s">
         <v>13</v>
       </c>
+      <c r="AW47" t="s">
+        <v>5</v>
+      </c>
       <c r="AX47" t="s">
-        <v>5</v>
-      </c>
-      <c r="AY47" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="BG47" t="s">
+        <v>33</v>
       </c>
       <c r="BH47" t="s">
         <v>33</v>
@@ -2475,12 +2472,9 @@
         <v>33</v>
       </c>
       <c r="BK47" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="BL47" t="s">
-        <v>14</v>
-      </c>
-      <c r="BM47" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2494,16 +2488,16 @@
       <c r="C48" t="s">
         <v>26</v>
       </c>
+      <c r="AW48" t="s">
+        <v>5</v>
+      </c>
       <c r="AX48" t="s">
-        <v>5</v>
-      </c>
-      <c r="AY48" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="BK48" t="s">
+        <v>14</v>
       </c>
       <c r="BL48" t="s">
-        <v>14</v>
-      </c>
-      <c r="BM48" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2517,19 +2511,19 @@
       <c r="C49" t="s">
         <v>27</v>
       </c>
+      <c r="AX49" t="s">
+        <v>5</v>
+      </c>
       <c r="AY49" t="s">
-        <v>5</v>
-      </c>
-      <c r="AZ49" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="BK49" t="s">
+        <v>15</v>
       </c>
       <c r="BL49" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BM49" t="s">
-        <v>14</v>
-      </c>
-      <c r="BN49" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2543,15 +2537,18 @@
       <c r="C50" t="s">
         <v>28</v>
       </c>
+      <c r="AX50" t="s">
+        <v>5</v>
+      </c>
       <c r="AY50" t="s">
-        <v>5</v>
-      </c>
-      <c r="AZ50" t="s">
-        <v>9</v>
-      </c>
-      <c r="BL50" t="s">
+        <v>9</v>
+      </c>
+      <c r="BK50" t="s">
         <v>34</v>
       </c>
+      <c r="BM50" t="s">
+        <v>14</v>
+      </c>
       <c r="BN50" t="s">
         <v>14</v>
       </c>
@@ -2562,9 +2559,6 @@
         <v>14</v>
       </c>
       <c r="BQ50" t="s">
-        <v>14</v>
-      </c>
-      <c r="BR50" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2578,15 +2572,18 @@
       <c r="C51" t="s">
         <v>29</v>
       </c>
+      <c r="AX51" t="s">
+        <v>5</v>
+      </c>
       <c r="AY51" t="s">
-        <v>5</v>
-      </c>
-      <c r="AZ51" t="s">
-        <v>9</v>
-      </c>
-      <c r="BM51" t="s">
+        <v>9</v>
+      </c>
+      <c r="BL51" t="s">
         <v>34</v>
       </c>
+      <c r="BQ51" t="s">
+        <v>14</v>
+      </c>
       <c r="BR51" t="s">
         <v>14</v>
       </c>
@@ -2594,9 +2591,6 @@
         <v>14</v>
       </c>
       <c r="BT51" t="s">
-        <v>14</v>
-      </c>
-      <c r="BU51" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2610,19 +2604,19 @@
       <c r="C52" t="s">
         <v>30</v>
       </c>
+      <c r="AX52" t="s">
+        <v>5</v>
+      </c>
       <c r="AY52" t="s">
-        <v>5</v>
-      </c>
-      <c r="AZ52" t="s">
-        <v>9</v>
-      </c>
-      <c r="BM52" t="s">
+        <v>9</v>
+      </c>
+      <c r="BL52" t="s">
         <v>34</v>
       </c>
+      <c r="BT52" t="s">
+        <v>14</v>
+      </c>
       <c r="BU52" t="s">
-        <v>14</v>
-      </c>
-      <c r="BV52" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2636,22 +2630,22 @@
       <c r="C53" t="s">
         <v>31</v>
       </c>
+      <c r="AY53" t="s">
+        <v>5</v>
+      </c>
       <c r="AZ53" t="s">
-        <v>5</v>
-      </c>
-      <c r="BA53" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="BL53" t="s">
+        <v>33</v>
       </c>
       <c r="BM53" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="BN53" t="s">
-        <v>14</v>
-      </c>
-      <c r="BO53" t="s">
         <v>21</v>
       </c>
-      <c r="BV53" t="s">
+      <c r="BU53" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2665,11 +2659,14 @@
       <c r="C54" t="s">
         <v>32</v>
       </c>
+      <c r="AY54" t="s">
+        <v>5</v>
+      </c>
       <c r="AZ54" t="s">
-        <v>5</v>
-      </c>
-      <c r="BA54" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="BM54" t="s">
+        <v>33</v>
       </c>
       <c r="BN54" t="s">
         <v>33</v>
@@ -2681,18 +2678,12 @@
         <v>33</v>
       </c>
       <c r="BQ54" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="BR54" t="s">
-        <v>34</v>
-      </c>
-      <c r="BS54" t="s">
-        <v>14</v>
-      </c>
-      <c r="BT54" t="s">
         <v>21</v>
       </c>
-      <c r="BV54" t="s">
+      <c r="BU54" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2706,11 +2697,14 @@
       <c r="C55" t="s">
         <v>27</v>
       </c>
+      <c r="AZ55" t="s">
+        <v>5</v>
+      </c>
       <c r="BA55" t="s">
-        <v>5</v>
-      </c>
-      <c r="BB55" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="BQ55" t="s">
+        <v>33</v>
       </c>
       <c r="BR55" t="s">
         <v>33</v>
@@ -2719,15 +2713,12 @@
         <v>33</v>
       </c>
       <c r="BT55" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="BU55" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BV55" t="s">
-        <v>14</v>
-      </c>
-      <c r="BW55" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2741,17 +2732,20 @@
       <c r="C56" t="s">
         <v>28</v>
       </c>
+      <c r="AZ56" t="s">
+        <v>5</v>
+      </c>
       <c r="BA56" t="s">
-        <v>5</v>
-      </c>
-      <c r="BB56" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="BT56" t="s">
+        <v>33</v>
       </c>
       <c r="BU56" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="BV56" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="BW56" t="s">
         <v>14</v>
@@ -2763,9 +2757,6 @@
         <v>14</v>
       </c>
       <c r="BZ56" t="s">
-        <v>14</v>
-      </c>
-      <c r="CA56" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2779,15 +2770,18 @@
       <c r="C57" t="s">
         <v>29</v>
       </c>
-      <c r="BA57" t="s">
-        <v>5</v>
-      </c>
-      <c r="BD57" t="s">
-        <v>9</v>
-      </c>
-      <c r="BV57" t="s">
+      <c r="AZ57" t="s">
+        <v>5</v>
+      </c>
+      <c r="BC57" t="s">
+        <v>9</v>
+      </c>
+      <c r="BU57" t="s">
         <v>34</v>
       </c>
+      <c r="BZ57" t="s">
+        <v>14</v>
+      </c>
       <c r="CA57" t="s">
         <v>14</v>
       </c>
@@ -2795,9 +2789,6 @@
         <v>14</v>
       </c>
       <c r="CC57" t="s">
-        <v>14</v>
-      </c>
-      <c r="CD57" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2811,19 +2802,19 @@
       <c r="C58" t="s">
         <v>30</v>
       </c>
-      <c r="BA58" t="s">
-        <v>5</v>
-      </c>
-      <c r="BD58" t="s">
-        <v>9</v>
-      </c>
-      <c r="BV58" t="s">
+      <c r="AZ58" t="s">
+        <v>5</v>
+      </c>
+      <c r="BC58" t="s">
+        <v>9</v>
+      </c>
+      <c r="BU58" t="s">
         <v>34</v>
       </c>
+      <c r="CC58" t="s">
+        <v>14</v>
+      </c>
       <c r="CD58" t="s">
-        <v>14</v>
-      </c>
-      <c r="CE58" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2837,22 +2828,22 @@
       <c r="C59" t="s">
         <v>31</v>
       </c>
-      <c r="BB59" t="s">
-        <v>5</v>
-      </c>
-      <c r="BD59" t="s">
-        <v>9</v>
+      <c r="BA59" t="s">
+        <v>5</v>
+      </c>
+      <c r="BC59" t="s">
+        <v>9</v>
+      </c>
+      <c r="BU59" t="s">
+        <v>33</v>
       </c>
       <c r="BV59" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="BW59" t="s">
-        <v>14</v>
-      </c>
-      <c r="BX59" t="s">
         <v>21</v>
       </c>
-      <c r="CE59" t="s">
+      <c r="CD59" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2866,11 +2857,14 @@
       <c r="C60" t="s">
         <v>32</v>
       </c>
-      <c r="BB60" t="s">
-        <v>5</v>
-      </c>
-      <c r="BD60" t="s">
-        <v>9</v>
+      <c r="BA60" t="s">
+        <v>5</v>
+      </c>
+      <c r="BC60" t="s">
+        <v>9</v>
+      </c>
+      <c r="BV60" t="s">
+        <v>33</v>
       </c>
       <c r="BW60" t="s">
         <v>33</v>
@@ -2882,18 +2876,12 @@
         <v>33</v>
       </c>
       <c r="BZ60" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="CA60" t="s">
-        <v>34</v>
-      </c>
-      <c r="CB60" t="s">
-        <v>14</v>
-      </c>
-      <c r="CC60" t="s">
         <v>21</v>
       </c>
-      <c r="CE60" t="s">
+      <c r="CD60" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2907,11 +2895,14 @@
       <c r="C61" t="s">
         <v>27</v>
       </c>
+      <c r="BC61" t="s">
+        <v>5</v>
+      </c>
       <c r="BD61" t="s">
-        <v>5</v>
-      </c>
-      <c r="BE61" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="BZ61" t="s">
+        <v>33</v>
       </c>
       <c r="CA61" t="s">
         <v>33</v>
@@ -2920,15 +2911,12 @@
         <v>33</v>
       </c>
       <c r="CC61" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="CD61" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="CE61" t="s">
-        <v>14</v>
-      </c>
-      <c r="CF61" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2942,17 +2930,20 @@
       <c r="C62" t="s">
         <v>28</v>
       </c>
-      <c r="BD62" t="s">
-        <v>5</v>
-      </c>
-      <c r="BH62" t="s">
-        <v>9</v>
+      <c r="BC62" t="s">
+        <v>5</v>
+      </c>
+      <c r="BG62" t="s">
+        <v>9</v>
+      </c>
+      <c r="CC62" t="s">
+        <v>33</v>
       </c>
       <c r="CD62" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="CE62" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="CF62" t="s">
         <v>14</v>
@@ -2964,9 +2955,6 @@
         <v>14</v>
       </c>
       <c r="CI62" t="s">
-        <v>14</v>
-      </c>
-      <c r="CJ62" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2980,15 +2968,18 @@
       <c r="C63" t="s">
         <v>29</v>
       </c>
-      <c r="BD63" t="s">
-        <v>5</v>
-      </c>
-      <c r="BL63" t="s">
-        <v>9</v>
-      </c>
-      <c r="CE63" t="s">
+      <c r="BC63" t="s">
+        <v>5</v>
+      </c>
+      <c r="BK63" t="s">
+        <v>9</v>
+      </c>
+      <c r="CD63" t="s">
         <v>34</v>
       </c>
+      <c r="CI63" t="s">
+        <v>14</v>
+      </c>
       <c r="CJ63" t="s">
         <v>14</v>
       </c>
@@ -2996,9 +2987,6 @@
         <v>14</v>
       </c>
       <c r="CL63" t="s">
-        <v>14</v>
-      </c>
-      <c r="CM63" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3012,19 +3000,19 @@
       <c r="C64" t="s">
         <v>30</v>
       </c>
-      <c r="BD64" t="s">
-        <v>5</v>
-      </c>
-      <c r="BL64" t="s">
-        <v>9</v>
-      </c>
-      <c r="CE64" t="s">
+      <c r="BC64" t="s">
+        <v>5</v>
+      </c>
+      <c r="BK64" t="s">
+        <v>9</v>
+      </c>
+      <c r="CD64" t="s">
         <v>34</v>
       </c>
+      <c r="CL64" t="s">
+        <v>14</v>
+      </c>
       <c r="CM64" t="s">
-        <v>14</v>
-      </c>
-      <c r="CN64" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3038,22 +3026,22 @@
       <c r="C65" t="s">
         <v>31</v>
       </c>
-      <c r="BE65" t="s">
-        <v>5</v>
-      </c>
-      <c r="BL65" t="s">
-        <v>9</v>
+      <c r="BD65" t="s">
+        <v>5</v>
+      </c>
+      <c r="BK65" t="s">
+        <v>9</v>
+      </c>
+      <c r="CD65" t="s">
+        <v>33</v>
       </c>
       <c r="CE65" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="CF65" t="s">
-        <v>14</v>
-      </c>
-      <c r="CG65" t="s">
         <v>21</v>
       </c>
-      <c r="CN65" t="s">
+      <c r="CM65" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3067,11 +3055,14 @@
       <c r="C66" t="s">
         <v>32</v>
       </c>
-      <c r="BH66" t="s">
-        <v>5</v>
-      </c>
-      <c r="BL66" t="s">
-        <v>9</v>
+      <c r="BG66" t="s">
+        <v>5</v>
+      </c>
+      <c r="BK66" t="s">
+        <v>9</v>
+      </c>
+      <c r="CE66" t="s">
+        <v>33</v>
       </c>
       <c r="CF66" t="s">
         <v>33</v>
@@ -3083,18 +3074,12 @@
         <v>33</v>
       </c>
       <c r="CI66" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="CJ66" t="s">
-        <v>34</v>
-      </c>
-      <c r="CK66" t="s">
-        <v>14</v>
-      </c>
-      <c r="CL66" t="s">
         <v>21</v>
       </c>
-      <c r="CN66" t="s">
+      <c r="CM66" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3108,22 +3093,22 @@
       <c r="C67" t="s">
         <v>35</v>
       </c>
+      <c r="CJ67" t="s">
+        <v>5</v>
+      </c>
+      <c r="CK67" t="s">
+        <v>9</v>
+      </c>
       <c r="CL67" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="CM67" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="CN67" t="s">
         <v>14</v>
       </c>
       <c r="CO67" t="s">
-        <v>14</v>
-      </c>
-      <c r="CP67" t="s">
-        <v>14</v>
-      </c>
-      <c r="CQ67" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3137,25 +3122,28 @@
       <c r="C68" t="s">
         <v>36</v>
       </c>
+      <c r="CJ68" t="s">
+        <v>5</v>
+      </c>
+      <c r="CK68" t="s">
+        <v>9</v>
+      </c>
       <c r="CL68" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="CM68" t="s">
-        <v>9</v>
-      </c>
-      <c r="CN68" t="s">
         <v>34</v>
       </c>
+      <c r="CO68" t="s">
+        <v>14</v>
+      </c>
+      <c r="CP68" t="s">
+        <v>14</v>
+      </c>
       <c r="CQ68" t="s">
         <v>14</v>
       </c>
       <c r="CR68" t="s">
-        <v>14</v>
-      </c>
-      <c r="CS68" t="s">
-        <v>14</v>
-      </c>
-      <c r="CT68" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3169,19 +3157,19 @@
       <c r="C69" t="s">
         <v>37</v>
       </c>
-      <c r="CL69" t="s">
-        <v>5</v>
+      <c r="CJ69" t="s">
+        <v>5</v>
+      </c>
+      <c r="CK69" t="s">
+        <v>9</v>
       </c>
       <c r="CM69" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="CN69" t="s">
-        <v>14</v>
-      </c>
-      <c r="CO69" t="s">
         <v>21</v>
       </c>
-      <c r="CT69" t="s">
+      <c r="CR69" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3195,19 +3183,19 @@
       <c r="C70" t="s">
         <v>38</v>
       </c>
-      <c r="CL70" t="s">
-        <v>5</v>
+      <c r="CJ70" t="s">
+        <v>5</v>
+      </c>
+      <c r="CK70" t="s">
+        <v>9</v>
       </c>
       <c r="CM70" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="CN70" t="s">
-        <v>14</v>
-      </c>
-      <c r="CO70" t="s">
         <v>21</v>
       </c>
-      <c r="CT70" t="s">
+      <c r="CR70" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3221,31 +3209,31 @@
       <c r="C71" t="s">
         <v>18</v>
       </c>
+      <c r="CK71" t="s">
+        <v>5</v>
+      </c>
+      <c r="CL71" t="s">
+        <v>9</v>
+      </c>
       <c r="CM71" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="CN71" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="CO71" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="CP71" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="CQ71" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="CR71" t="s">
         <v>14</v>
       </c>
       <c r="CS71" t="s">
-        <v>14</v>
-      </c>
-      <c r="CT71" t="s">
-        <v>14</v>
-      </c>
-      <c r="CU71" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3259,34 +3247,34 @@
       <c r="C72" t="s">
         <v>19</v>
       </c>
-      <c r="CM72" t="s">
-        <v>5</v>
-      </c>
-      <c r="CN72" t="s">
-        <v>9</v>
+      <c r="CK72" t="s">
+        <v>5</v>
+      </c>
+      <c r="CL72" t="s">
+        <v>9</v>
+      </c>
+      <c r="CO72" t="s">
+        <v>33</v>
+      </c>
+      <c r="CP72" t="s">
+        <v>33</v>
       </c>
       <c r="CQ72" t="s">
         <v>33</v>
       </c>
       <c r="CR72" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="CS72" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="CT72" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="CU72" t="s">
         <v>14</v>
       </c>
       <c r="CV72" t="s">
-        <v>14</v>
-      </c>
-      <c r="CW72" t="s">
-        <v>14</v>
-      </c>
-      <c r="CX72" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3300,15 +3288,21 @@
       <c r="C73" t="s">
         <v>20</v>
       </c>
-      <c r="CM73" t="s">
-        <v>5</v>
-      </c>
-      <c r="CN73" t="s">
-        <v>9</v>
-      </c>
-      <c r="CT73" t="s">
+      <c r="CK73" t="s">
+        <v>5</v>
+      </c>
+      <c r="CL73" t="s">
+        <v>9</v>
+      </c>
+      <c r="CR73" t="s">
         <v>34</v>
       </c>
+      <c r="CV73" t="s">
+        <v>14</v>
+      </c>
+      <c r="CW73" t="s">
+        <v>14</v>
+      </c>
       <c r="CX73" t="s">
         <v>14</v>
       </c>
@@ -3316,12 +3310,6 @@
         <v>14</v>
       </c>
       <c r="CZ73" t="s">
-        <v>14</v>
-      </c>
-      <c r="DA73" t="s">
-        <v>14</v>
-      </c>
-      <c r="DB73" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3335,11 +3323,17 @@
       <c r="C74" t="s">
         <v>23</v>
       </c>
-      <c r="CM74" t="s">
-        <v>5</v>
-      </c>
-      <c r="CN74" t="s">
-        <v>9</v>
+      <c r="CK74" t="s">
+        <v>5</v>
+      </c>
+      <c r="CL74" t="s">
+        <v>9</v>
+      </c>
+      <c r="CR74" t="s">
+        <v>14</v>
+      </c>
+      <c r="CS74" t="s">
+        <v>14</v>
       </c>
       <c r="CT74" t="s">
         <v>14</v>
@@ -3348,15 +3342,9 @@
         <v>14</v>
       </c>
       <c r="CV74" t="s">
-        <v>14</v>
-      </c>
-      <c r="CW74" t="s">
-        <v>14</v>
-      </c>
-      <c r="CX74" t="s">
         <v>21</v>
       </c>
-      <c r="DB74" t="s">
+      <c r="CZ74" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3370,14 +3358,20 @@
       <c r="C75" t="s">
         <v>24</v>
       </c>
-      <c r="CN75" t="s">
-        <v>5</v>
-      </c>
-      <c r="CO75" t="s">
-        <v>9</v>
+      <c r="CL75" t="s">
+        <v>5</v>
+      </c>
+      <c r="CM75" t="s">
+        <v>9</v>
+      </c>
+      <c r="CR75" t="s">
+        <v>33</v>
+      </c>
+      <c r="CS75" t="s">
+        <v>14</v>
       </c>
       <c r="CT75" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="CU75" t="s">
         <v>14</v>
@@ -3392,15 +3386,9 @@
         <v>14</v>
       </c>
       <c r="CY75" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="CZ75" t="s">
-        <v>14</v>
-      </c>
-      <c r="DA75" t="s">
-        <v>21</v>
-      </c>
-      <c r="DB75" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3414,28 +3402,28 @@
       <c r="C76" t="s">
         <v>25</v>
       </c>
-      <c r="CN76" t="s">
-        <v>5</v>
-      </c>
-      <c r="CO76" t="s">
-        <v>9</v>
+      <c r="CL76" t="s">
+        <v>5</v>
+      </c>
+      <c r="CM76" t="s">
+        <v>9</v>
+      </c>
+      <c r="CS76" t="s">
+        <v>33</v>
+      </c>
+      <c r="CT76" t="s">
+        <v>33</v>
       </c>
       <c r="CU76" t="s">
         <v>33</v>
       </c>
       <c r="CV76" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="CW76" t="s">
-        <v>33</v>
-      </c>
-      <c r="CX76" t="s">
-        <v>14</v>
-      </c>
-      <c r="CY76" t="s">
         <v>21</v>
       </c>
-      <c r="DB76" t="s">
+      <c r="CZ76" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3449,11 +3437,17 @@
       <c r="C77" t="s">
         <v>13</v>
       </c>
-      <c r="CN77" t="s">
-        <v>5</v>
-      </c>
-      <c r="CO77" t="s">
-        <v>9</v>
+      <c r="CL77" t="s">
+        <v>5</v>
+      </c>
+      <c r="CM77" t="s">
+        <v>9</v>
+      </c>
+      <c r="CV77" t="s">
+        <v>33</v>
+      </c>
+      <c r="CW77" t="s">
+        <v>33</v>
       </c>
       <c r="CX77" t="s">
         <v>33</v>
@@ -3462,15 +3456,9 @@
         <v>33</v>
       </c>
       <c r="CZ77" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="DA77" t="s">
-        <v>33</v>
-      </c>
-      <c r="DB77" t="s">
-        <v>14</v>
-      </c>
-      <c r="DC77" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3484,16 +3472,16 @@
       <c r="C78" t="s">
         <v>26</v>
       </c>
-      <c r="CN78" t="s">
-        <v>5</v>
-      </c>
-      <c r="CO78" t="s">
-        <v>9</v>
-      </c>
-      <c r="DB78" t="s">
-        <v>14</v>
-      </c>
-      <c r="DC78" t="s">
+      <c r="CL78" t="s">
+        <v>5</v>
+      </c>
+      <c r="CM78" t="s">
+        <v>9</v>
+      </c>
+      <c r="CZ78" t="s">
+        <v>14</v>
+      </c>
+      <c r="DA78" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3507,19 +3495,19 @@
       <c r="C79" t="s">
         <v>27</v>
       </c>
-      <c r="CO79" t="s">
-        <v>5</v>
-      </c>
-      <c r="CP79" t="s">
-        <v>9</v>
+      <c r="CM79" t="s">
+        <v>5</v>
+      </c>
+      <c r="CN79" t="s">
+        <v>9</v>
+      </c>
+      <c r="CZ79" t="s">
+        <v>15</v>
+      </c>
+      <c r="DA79" t="s">
+        <v>14</v>
       </c>
       <c r="DB79" t="s">
-        <v>15</v>
-      </c>
-      <c r="DC79" t="s">
-        <v>14</v>
-      </c>
-      <c r="DD79" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3533,14 +3521,20 @@
       <c r="C80" t="s">
         <v>28</v>
       </c>
-      <c r="CO80" t="s">
-        <v>5</v>
-      </c>
-      <c r="CP80" t="s">
-        <v>9</v>
+      <c r="CM80" t="s">
+        <v>5</v>
+      </c>
+      <c r="CN80" t="s">
+        <v>9</v>
+      </c>
+      <c r="CZ80" t="s">
+        <v>34</v>
       </c>
       <c r="DB80" t="s">
-        <v>34</v>
+        <v>14</v>
+      </c>
+      <c r="DC80" t="s">
+        <v>14</v>
       </c>
       <c r="DD80" t="s">
         <v>14</v>
@@ -3549,12 +3543,6 @@
         <v>14</v>
       </c>
       <c r="DF80" t="s">
-        <v>14</v>
-      </c>
-      <c r="DG80" t="s">
-        <v>14</v>
-      </c>
-      <c r="DH80" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3568,25 +3556,25 @@
       <c r="C81" t="s">
         <v>29</v>
       </c>
-      <c r="CO81" t="s">
-        <v>5</v>
-      </c>
-      <c r="CP81" t="s">
-        <v>9</v>
-      </c>
-      <c r="DC81" t="s">
+      <c r="CM81" t="s">
+        <v>5</v>
+      </c>
+      <c r="CN81" t="s">
+        <v>9</v>
+      </c>
+      <c r="DA81" t="s">
         <v>34</v>
       </c>
+      <c r="DF81" t="s">
+        <v>14</v>
+      </c>
+      <c r="DG81" t="s">
+        <v>14</v>
+      </c>
       <c r="DH81" t="s">
         <v>14</v>
       </c>
       <c r="DI81" t="s">
-        <v>14</v>
-      </c>
-      <c r="DJ81" t="s">
-        <v>14</v>
-      </c>
-      <c r="DK81" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3600,19 +3588,19 @@
       <c r="C82" t="s">
         <v>30</v>
       </c>
-      <c r="CO82" t="s">
-        <v>5</v>
-      </c>
-      <c r="CP82" t="s">
-        <v>9</v>
-      </c>
-      <c r="DC82" t="s">
+      <c r="CM82" t="s">
+        <v>5</v>
+      </c>
+      <c r="CN82" t="s">
+        <v>9</v>
+      </c>
+      <c r="DA82" t="s">
         <v>34</v>
       </c>
-      <c r="DK82" t="s">
-        <v>14</v>
-      </c>
-      <c r="DL82" t="s">
+      <c r="DI82" t="s">
+        <v>14</v>
+      </c>
+      <c r="DJ82" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3626,22 +3614,22 @@
       <c r="C83" t="s">
         <v>31</v>
       </c>
-      <c r="CP83" t="s">
-        <v>5</v>
-      </c>
-      <c r="CQ83" t="s">
-        <v>9</v>
+      <c r="CN83" t="s">
+        <v>5</v>
+      </c>
+      <c r="CO83" t="s">
+        <v>9</v>
+      </c>
+      <c r="DA83" t="s">
+        <v>33</v>
+      </c>
+      <c r="DB83" t="s">
+        <v>14</v>
       </c>
       <c r="DC83" t="s">
-        <v>33</v>
-      </c>
-      <c r="DD83" t="s">
-        <v>14</v>
-      </c>
-      <c r="DE83" t="s">
         <v>21</v>
       </c>
-      <c r="DL83" t="s">
+      <c r="DJ83" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3655,11 +3643,17 @@
       <c r="C84" t="s">
         <v>32</v>
       </c>
-      <c r="CP84" t="s">
-        <v>5</v>
-      </c>
-      <c r="CQ84" t="s">
-        <v>9</v>
+      <c r="CN84" t="s">
+        <v>5</v>
+      </c>
+      <c r="CO84" t="s">
+        <v>9</v>
+      </c>
+      <c r="DB84" t="s">
+        <v>33</v>
+      </c>
+      <c r="DC84" t="s">
+        <v>33</v>
       </c>
       <c r="DD84" t="s">
         <v>33</v>
@@ -3668,21 +3662,12 @@
         <v>33</v>
       </c>
       <c r="DF84" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="DG84" t="s">
-        <v>33</v>
-      </c>
-      <c r="DH84" t="s">
-        <v>34</v>
-      </c>
-      <c r="DI84" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="DJ84" t="s">
-        <v>21</v>
-      </c>
-      <c r="DL84" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3696,28 +3681,28 @@
       <c r="C85" t="s">
         <v>27</v>
       </c>
-      <c r="CQ85" t="s">
-        <v>5</v>
-      </c>
-      <c r="CR85" t="s">
-        <v>9</v>
+      <c r="CO85" t="s">
+        <v>5</v>
+      </c>
+      <c r="CP85" t="s">
+        <v>9</v>
+      </c>
+      <c r="DF85" t="s">
+        <v>33</v>
+      </c>
+      <c r="DG85" t="s">
+        <v>33</v>
       </c>
       <c r="DH85" t="s">
         <v>33</v>
       </c>
       <c r="DI85" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="DJ85" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="DK85" t="s">
-        <v>15</v>
-      </c>
-      <c r="DL85" t="s">
-        <v>14</v>
-      </c>
-      <c r="DM85" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3731,17 +3716,23 @@
       <c r="C86" t="s">
         <v>28</v>
       </c>
-      <c r="CQ86" t="s">
-        <v>5</v>
-      </c>
-      <c r="CR86" t="s">
-        <v>9</v>
+      <c r="CO86" t="s">
+        <v>5</v>
+      </c>
+      <c r="CP86" t="s">
+        <v>9</v>
+      </c>
+      <c r="DI86" t="s">
+        <v>33</v>
+      </c>
+      <c r="DJ86" t="s">
+        <v>34</v>
       </c>
       <c r="DK86" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="DL86" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="DM86" t="s">
         <v>14</v>
@@ -3750,12 +3741,6 @@
         <v>14</v>
       </c>
       <c r="DO86" t="s">
-        <v>14</v>
-      </c>
-      <c r="DP86" t="s">
-        <v>14</v>
-      </c>
-      <c r="DQ86" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3769,25 +3754,25 @@
       <c r="C87" t="s">
         <v>29</v>
       </c>
-      <c r="CQ87" t="s">
-        <v>5</v>
-      </c>
-      <c r="CT87" t="s">
-        <v>9</v>
-      </c>
-      <c r="DL87" t="s">
+      <c r="CO87" t="s">
+        <v>5</v>
+      </c>
+      <c r="CR87" t="s">
+        <v>9</v>
+      </c>
+      <c r="DJ87" t="s">
         <v>34</v>
       </c>
+      <c r="DO87" t="s">
+        <v>14</v>
+      </c>
+      <c r="DP87" t="s">
+        <v>14</v>
+      </c>
       <c r="DQ87" t="s">
         <v>14</v>
       </c>
       <c r="DR87" t="s">
-        <v>14</v>
-      </c>
-      <c r="DS87" t="s">
-        <v>14</v>
-      </c>
-      <c r="DT87" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3801,19 +3786,19 @@
       <c r="C88" t="s">
         <v>30</v>
       </c>
-      <c r="CQ88" t="s">
-        <v>5</v>
-      </c>
-      <c r="CT88" t="s">
-        <v>9</v>
-      </c>
-      <c r="DL88" t="s">
+      <c r="CO88" t="s">
+        <v>5</v>
+      </c>
+      <c r="CR88" t="s">
+        <v>9</v>
+      </c>
+      <c r="DJ88" t="s">
         <v>34</v>
       </c>
-      <c r="DT88" t="s">
-        <v>14</v>
-      </c>
-      <c r="DU88" t="s">
+      <c r="DR88" t="s">
+        <v>14</v>
+      </c>
+      <c r="DS88" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3827,22 +3812,22 @@
       <c r="C89" t="s">
         <v>31</v>
       </c>
+      <c r="CP89" t="s">
+        <v>5</v>
+      </c>
       <c r="CR89" t="s">
-        <v>5</v>
-      </c>
-      <c r="CT89" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="DJ89" t="s">
+        <v>33</v>
+      </c>
+      <c r="DK89" t="s">
+        <v>14</v>
       </c>
       <c r="DL89" t="s">
-        <v>33</v>
-      </c>
-      <c r="DM89" t="s">
-        <v>14</v>
-      </c>
-      <c r="DN89" t="s">
         <v>21</v>
       </c>
-      <c r="DU89" t="s">
+      <c r="DS89" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3856,11 +3841,17 @@
       <c r="C90" t="s">
         <v>32</v>
       </c>
+      <c r="CP90" t="s">
+        <v>5</v>
+      </c>
       <c r="CR90" t="s">
-        <v>5</v>
-      </c>
-      <c r="CT90" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="DK90" t="s">
+        <v>33</v>
+      </c>
+      <c r="DL90" t="s">
+        <v>33</v>
       </c>
       <c r="DM90" t="s">
         <v>33</v>
@@ -3869,21 +3860,12 @@
         <v>33</v>
       </c>
       <c r="DO90" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="DP90" t="s">
-        <v>33</v>
-      </c>
-      <c r="DQ90" t="s">
-        <v>34</v>
-      </c>
-      <c r="DR90" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="DS90" t="s">
-        <v>21</v>
-      </c>
-      <c r="DU90" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3897,28 +3879,28 @@
       <c r="C91" t="s">
         <v>27</v>
       </c>
-      <c r="CT91" t="s">
-        <v>5</v>
-      </c>
-      <c r="CU91" t="s">
-        <v>9</v>
+      <c r="CR91" t="s">
+        <v>5</v>
+      </c>
+      <c r="CS91" t="s">
+        <v>9</v>
+      </c>
+      <c r="DO91" t="s">
+        <v>33</v>
+      </c>
+      <c r="DP91" t="s">
+        <v>33</v>
       </c>
       <c r="DQ91" t="s">
         <v>33</v>
       </c>
       <c r="DR91" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="DS91" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="DT91" t="s">
-        <v>15</v>
-      </c>
-      <c r="DU91" t="s">
-        <v>14</v>
-      </c>
-      <c r="DV91" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3932,17 +3914,23 @@
       <c r="C92" t="s">
         <v>28</v>
       </c>
-      <c r="CT92" t="s">
-        <v>5</v>
-      </c>
-      <c r="CX92" t="s">
-        <v>9</v>
+      <c r="CR92" t="s">
+        <v>5</v>
+      </c>
+      <c r="CV92" t="s">
+        <v>9</v>
+      </c>
+      <c r="DR92" t="s">
+        <v>33</v>
+      </c>
+      <c r="DS92" t="s">
+        <v>34</v>
       </c>
       <c r="DT92" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="DU92" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="DV92" t="s">
         <v>14</v>
@@ -3951,12 +3939,6 @@
         <v>14</v>
       </c>
       <c r="DX92" t="s">
-        <v>14</v>
-      </c>
-      <c r="DY92" t="s">
-        <v>14</v>
-      </c>
-      <c r="DZ92" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3970,25 +3952,25 @@
       <c r="C93" t="s">
         <v>29</v>
       </c>
-      <c r="CT93" t="s">
-        <v>5</v>
-      </c>
-      <c r="DB93" t="s">
-        <v>9</v>
-      </c>
-      <c r="DU93" t="s">
+      <c r="CR93" t="s">
+        <v>5</v>
+      </c>
+      <c r="CZ93" t="s">
+        <v>9</v>
+      </c>
+      <c r="DS93" t="s">
         <v>34</v>
       </c>
+      <c r="DX93" t="s">
+        <v>14</v>
+      </c>
+      <c r="DY93" t="s">
+        <v>14</v>
+      </c>
       <c r="DZ93" t="s">
         <v>14</v>
       </c>
       <c r="EA93" t="s">
-        <v>14</v>
-      </c>
-      <c r="EB93" t="s">
-        <v>14</v>
-      </c>
-      <c r="EC93" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4002,19 +3984,19 @@
       <c r="C94" t="s">
         <v>30</v>
       </c>
-      <c r="CT94" t="s">
-        <v>5</v>
-      </c>
-      <c r="DB94" t="s">
-        <v>9</v>
-      </c>
-      <c r="DU94" t="s">
+      <c r="CR94" t="s">
+        <v>5</v>
+      </c>
+      <c r="CZ94" t="s">
+        <v>9</v>
+      </c>
+      <c r="DS94" t="s">
         <v>34</v>
       </c>
-      <c r="EC94" t="s">
-        <v>14</v>
-      </c>
-      <c r="ED94" t="s">
+      <c r="EA94" t="s">
+        <v>14</v>
+      </c>
+      <c r="EB94" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4028,22 +4010,22 @@
       <c r="C95" t="s">
         <v>31</v>
       </c>
-      <c r="CU95" t="s">
-        <v>5</v>
-      </c>
-      <c r="DB95" t="s">
-        <v>9</v>
+      <c r="CS95" t="s">
+        <v>5</v>
+      </c>
+      <c r="CZ95" t="s">
+        <v>9</v>
+      </c>
+      <c r="DS95" t="s">
+        <v>33</v>
+      </c>
+      <c r="DT95" t="s">
+        <v>14</v>
       </c>
       <c r="DU95" t="s">
-        <v>33</v>
-      </c>
-      <c r="DV95" t="s">
-        <v>14</v>
-      </c>
-      <c r="DW95" t="s">
         <v>21</v>
       </c>
-      <c r="ED95" t="s">
+      <c r="EB95" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4057,11 +4039,17 @@
       <c r="C96" t="s">
         <v>32</v>
       </c>
-      <c r="CX96" t="s">
-        <v>5</v>
-      </c>
-      <c r="DB96" t="s">
-        <v>9</v>
+      <c r="CV96" t="s">
+        <v>5</v>
+      </c>
+      <c r="CZ96" t="s">
+        <v>9</v>
+      </c>
+      <c r="DT96" t="s">
+        <v>33</v>
+      </c>
+      <c r="DU96" t="s">
+        <v>33</v>
       </c>
       <c r="DV96" t="s">
         <v>33</v>
@@ -4070,21 +4058,12 @@
         <v>33</v>
       </c>
       <c r="DX96" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="DY96" t="s">
-        <v>33</v>
-      </c>
-      <c r="DZ96" t="s">
-        <v>34</v>
-      </c>
-      <c r="EA96" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="EB96" t="s">
-        <v>21</v>
-      </c>
-      <c r="ED96" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4098,22 +4077,22 @@
       <c r="C97" t="s">
         <v>35</v>
       </c>
+      <c r="DY97" t="s">
+        <v>5</v>
+      </c>
+      <c r="DZ97" t="s">
+        <v>9</v>
+      </c>
+      <c r="EA97" t="s">
+        <v>14</v>
+      </c>
       <c r="EB97" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="EC97" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="ED97" t="s">
-        <v>14</v>
-      </c>
-      <c r="EE97" t="s">
-        <v>14</v>
-      </c>
-      <c r="EF97" t="s">
-        <v>14</v>
-      </c>
-      <c r="EG97" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4127,25 +4106,28 @@
       <c r="C98" t="s">
         <v>36</v>
       </c>
+      <c r="DY98" t="s">
+        <v>5</v>
+      </c>
+      <c r="DZ98" t="s">
+        <v>9</v>
+      </c>
+      <c r="EA98" t="s">
+        <v>33</v>
+      </c>
       <c r="EB98" t="s">
-        <v>5</v>
-      </c>
-      <c r="EC98" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="ED98" t="s">
-        <v>34</v>
+        <v>14</v>
+      </c>
+      <c r="EE98" t="s">
+        <v>14</v>
+      </c>
+      <c r="EF98" t="s">
+        <v>14</v>
       </c>
       <c r="EG98" t="s">
-        <v>14</v>
-      </c>
-      <c r="EH98" t="s">
-        <v>14</v>
-      </c>
-      <c r="EI98" t="s">
-        <v>14</v>
-      </c>
-      <c r="EJ98" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4159,19 +4141,19 @@
       <c r="C99" t="s">
         <v>37</v>
       </c>
+      <c r="DY99" t="s">
+        <v>5</v>
+      </c>
+      <c r="DZ99" t="s">
+        <v>9</v>
+      </c>
       <c r="EB99" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="EC99" t="s">
-        <v>9</v>
-      </c>
-      <c r="ED99" t="s">
-        <v>14</v>
-      </c>
-      <c r="EE99" t="s">
         <v>21</v>
       </c>
-      <c r="EJ99" t="s">
+      <c r="EG99" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4185,16 +4167,16 @@
       <c r="C100" t="s">
         <v>38</v>
       </c>
+      <c r="DY100" t="s">
+        <v>5</v>
+      </c>
       <c r="EB100" t="s">
-        <v>5</v>
-      </c>
-      <c r="ED100" t="s">
-        <v>14</v>
-      </c>
-      <c r="EE100" t="s">
+        <v>14</v>
+      </c>
+      <c r="EC100" t="s">
         <v>21</v>
       </c>
-      <c r="EJ100" t="s">
+      <c r="EG100" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4208,25 +4190,25 @@
       <c r="C101" t="s">
         <v>39</v>
       </c>
+      <c r="DZ101" t="s">
+        <v>5</v>
+      </c>
+      <c r="EA101" t="s">
+        <v>9</v>
+      </c>
+      <c r="EB101" t="s">
+        <v>33</v>
+      </c>
       <c r="EC101" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="ED101" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="EE101" t="s">
-        <v>33</v>
-      </c>
-      <c r="EF101" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="EG101" t="s">
-        <v>14</v>
-      </c>
-      <c r="EH101" t="s">
-        <v>21</v>
-      </c>
-      <c r="EJ101" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4240,25 +4222,25 @@
       <c r="C102" t="s">
         <v>40</v>
       </c>
-      <c r="EC102" t="s">
-        <v>5</v>
+      <c r="DZ102" t="s">
+        <v>5</v>
+      </c>
+      <c r="EA102" t="s">
+        <v>9</v>
       </c>
       <c r="ED102" t="s">
-        <v>9</v>
+        <v>33</v>
+      </c>
+      <c r="EE102" t="s">
+        <v>33</v>
+      </c>
+      <c r="EF102" t="s">
+        <v>33</v>
       </c>
       <c r="EG102" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="EH102" t="s">
-        <v>33</v>
-      </c>
-      <c r="EI102" t="s">
-        <v>33</v>
-      </c>
-      <c r="EJ102" t="s">
-        <v>14</v>
-      </c>
-      <c r="EK102" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4272,19 +4254,19 @@
       <c r="C103" t="s">
         <v>41</v>
       </c>
-      <c r="EC103" t="s">
-        <v>5</v>
-      </c>
-      <c r="ED103" t="s">
-        <v>9</v>
-      </c>
-      <c r="EJ103" t="s">
+      <c r="DZ103" t="s">
+        <v>5</v>
+      </c>
+      <c r="EA103" t="s">
+        <v>9</v>
+      </c>
+      <c r="EG103" t="s">
         <v>15</v>
       </c>
-      <c r="EK103" t="s">
-        <v>14</v>
-      </c>
-      <c r="EL103" t="s">
+      <c r="EH103" t="s">
+        <v>14</v>
+      </c>
+      <c r="EI103" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4298,22 +4280,22 @@
       <c r="C104" t="s">
         <v>42</v>
       </c>
-      <c r="EC104" t="s">
-        <v>5</v>
-      </c>
-      <c r="ED104" t="s">
-        <v>9</v>
+      <c r="DZ104" t="s">
+        <v>5</v>
+      </c>
+      <c r="EA104" t="s">
+        <v>9</v>
+      </c>
+      <c r="EG104" t="s">
+        <v>16</v>
+      </c>
+      <c r="EH104" t="s">
+        <v>15</v>
+      </c>
+      <c r="EI104" t="s">
+        <v>14</v>
       </c>
       <c r="EJ104" t="s">
-        <v>16</v>
-      </c>
-      <c r="EK104" t="s">
-        <v>15</v>
-      </c>
-      <c r="EL104" t="s">
-        <v>14</v>
-      </c>
-      <c r="EM104" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4327,22 +4309,22 @@
       <c r="C105" t="s">
         <v>43</v>
       </c>
-      <c r="ED105" t="s">
-        <v>5</v>
-      </c>
-      <c r="EE105" t="s">
-        <v>9</v>
+      <c r="EA105" t="s">
+        <v>5</v>
+      </c>
+      <c r="EB105" t="s">
+        <v>9</v>
+      </c>
+      <c r="EH105" t="s">
+        <v>16</v>
+      </c>
+      <c r="EI105" t="s">
+        <v>15</v>
+      </c>
+      <c r="EJ105" t="s">
+        <v>14</v>
       </c>
       <c r="EK105" t="s">
-        <v>16</v>
-      </c>
-      <c r="EL105" t="s">
-        <v>15</v>
-      </c>
-      <c r="EM105" t="s">
-        <v>14</v>
-      </c>
-      <c r="EN105" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4356,22 +4338,22 @@
       <c r="C106" t="s">
         <v>44</v>
       </c>
-      <c r="ED106" t="s">
-        <v>5</v>
-      </c>
-      <c r="EE106" t="s">
-        <v>9</v>
+      <c r="EA106" t="s">
+        <v>5</v>
+      </c>
+      <c r="EB106" t="s">
+        <v>9</v>
+      </c>
+      <c r="EI106" t="s">
+        <v>16</v>
+      </c>
+      <c r="EJ106" t="s">
+        <v>15</v>
+      </c>
+      <c r="EK106" t="s">
+        <v>14</v>
       </c>
       <c r="EL106" t="s">
-        <v>16</v>
-      </c>
-      <c r="EM106" t="s">
-        <v>15</v>
-      </c>
-      <c r="EN106" t="s">
-        <v>14</v>
-      </c>
-      <c r="EO106" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4385,22 +4367,22 @@
       <c r="C107" t="s">
         <v>45</v>
       </c>
-      <c r="ED107" t="s">
-        <v>5</v>
-      </c>
-      <c r="EE107" t="s">
-        <v>9</v>
+      <c r="EA107" t="s">
+        <v>5</v>
+      </c>
+      <c r="EB107" t="s">
+        <v>9</v>
+      </c>
+      <c r="EJ107" t="s">
+        <v>16</v>
+      </c>
+      <c r="EK107" t="s">
+        <v>15</v>
+      </c>
+      <c r="EL107" t="s">
+        <v>14</v>
       </c>
       <c r="EM107" t="s">
-        <v>16</v>
-      </c>
-      <c r="EN107" t="s">
-        <v>15</v>
-      </c>
-      <c r="EO107" t="s">
-        <v>14</v>
-      </c>
-      <c r="EP107" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4414,22 +4396,22 @@
       <c r="C108" t="s">
         <v>46</v>
       </c>
-      <c r="ED108" t="s">
-        <v>5</v>
-      </c>
-      <c r="EE108" t="s">
-        <v>9</v>
+      <c r="EA108" t="s">
+        <v>5</v>
+      </c>
+      <c r="EB108" t="s">
+        <v>9</v>
+      </c>
+      <c r="EK108" t="s">
+        <v>16</v>
+      </c>
+      <c r="EL108" t="s">
+        <v>15</v>
+      </c>
+      <c r="EM108" t="s">
+        <v>14</v>
       </c>
       <c r="EN108" t="s">
-        <v>16</v>
-      </c>
-      <c r="EO108" t="s">
-        <v>15</v>
-      </c>
-      <c r="EP108" t="s">
-        <v>14</v>
-      </c>
-      <c r="EQ108" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4443,22 +4425,22 @@
       <c r="C109" t="s">
         <v>47</v>
       </c>
-      <c r="EE109" t="s">
-        <v>5</v>
-      </c>
-      <c r="EF109" t="s">
-        <v>9</v>
+      <c r="EB109" t="s">
+        <v>5</v>
+      </c>
+      <c r="EC109" t="s">
+        <v>9</v>
+      </c>
+      <c r="EL109" t="s">
+        <v>16</v>
+      </c>
+      <c r="EM109" t="s">
+        <v>15</v>
+      </c>
+      <c r="EN109" t="s">
+        <v>14</v>
       </c>
       <c r="EO109" t="s">
-        <v>16</v>
-      </c>
-      <c r="EP109" t="s">
-        <v>15</v>
-      </c>
-      <c r="EQ109" t="s">
-        <v>14</v>
-      </c>
-      <c r="ER109" t="s">
         <v>22</v>
       </c>
     </row>

--- a/project/outputs_xlsx_solution/test33.4-wide-NR-4.xlsx
+++ b/project/outputs_xlsx_solution/test33.4-wide-NR-4.xlsx
@@ -2205,6 +2205,9 @@
       <c r="AU40" t="s">
         <v>5</v>
       </c>
+      <c r="AV40" t="s">
+        <v>9</v>
+      </c>
       <c r="AX40" t="s">
         <v>14</v>
       </c>
@@ -2225,20 +2228,11 @@
       <c r="C41" t="s">
         <v>18</v>
       </c>
-      <c r="AV41" t="s">
-        <v>5</v>
-      </c>
-      <c r="AW41" t="s">
-        <v>9</v>
-      </c>
-      <c r="AX41" t="s">
-        <v>33</v>
-      </c>
       <c r="AY41" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="AZ41" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="BA41" t="s">
         <v>14</v>
@@ -2263,14 +2257,11 @@
       <c r="C42" t="s">
         <v>19</v>
       </c>
-      <c r="AV42" t="s">
-        <v>5</v>
-      </c>
-      <c r="AW42" t="s">
-        <v>9</v>
+      <c r="AY42" t="s">
+        <v>5</v>
       </c>
       <c r="AZ42" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="BA42" t="s">
         <v>33</v>
@@ -2304,10 +2295,10 @@
       <c r="C43" t="s">
         <v>20</v>
       </c>
-      <c r="AV43" t="s">
-        <v>5</v>
-      </c>
-      <c r="AW43" t="s">
+      <c r="AY43" t="s">
+        <v>5</v>
+      </c>
+      <c r="AZ43" t="s">
         <v>9</v>
       </c>
       <c r="BC43" t="s">
@@ -2339,10 +2330,10 @@
       <c r="C44" t="s">
         <v>23</v>
       </c>
-      <c r="AV44" t="s">
-        <v>5</v>
-      </c>
-      <c r="AW44" t="s">
+      <c r="AY44" t="s">
+        <v>5</v>
+      </c>
+      <c r="AZ44" t="s">
         <v>9</v>
       </c>
       <c r="BC44" t="s">
@@ -2374,10 +2365,10 @@
       <c r="C45" t="s">
         <v>24</v>
       </c>
-      <c r="AW45" t="s">
-        <v>5</v>
-      </c>
-      <c r="AX45" t="s">
+      <c r="AZ45" t="s">
+        <v>5</v>
+      </c>
+      <c r="BA45" t="s">
         <v>9</v>
       </c>
       <c r="BC45" t="s">
@@ -2418,10 +2409,10 @@
       <c r="C46" t="s">
         <v>25</v>
       </c>
-      <c r="AW46" t="s">
-        <v>5</v>
-      </c>
-      <c r="AX46" t="s">
+      <c r="AZ46" t="s">
+        <v>5</v>
+      </c>
+      <c r="BA46" t="s">
         <v>9</v>
       </c>
       <c r="BD46" t="s">
@@ -2453,10 +2444,10 @@
       <c r="C47" t="s">
         <v>13</v>
       </c>
-      <c r="AW47" t="s">
-        <v>5</v>
-      </c>
-      <c r="AX47" t="s">
+      <c r="AZ47" t="s">
+        <v>5</v>
+      </c>
+      <c r="BA47" t="s">
         <v>9</v>
       </c>
       <c r="BG47" t="s">
@@ -2488,10 +2479,10 @@
       <c r="C48" t="s">
         <v>26</v>
       </c>
-      <c r="AW48" t="s">
-        <v>5</v>
-      </c>
-      <c r="AX48" t="s">
+      <c r="AZ48" t="s">
+        <v>5</v>
+      </c>
+      <c r="BA48" t="s">
         <v>9</v>
       </c>
       <c r="BK48" t="s">
@@ -2511,10 +2502,10 @@
       <c r="C49" t="s">
         <v>27</v>
       </c>
-      <c r="AX49" t="s">
-        <v>5</v>
-      </c>
-      <c r="AY49" t="s">
+      <c r="BA49" t="s">
+        <v>5</v>
+      </c>
+      <c r="BB49" t="s">
         <v>9</v>
       </c>
       <c r="BK49" t="s">
@@ -2537,10 +2528,10 @@
       <c r="C50" t="s">
         <v>28</v>
       </c>
-      <c r="AX50" t="s">
-        <v>5</v>
-      </c>
-      <c r="AY50" t="s">
+      <c r="BA50" t="s">
+        <v>5</v>
+      </c>
+      <c r="BB50" t="s">
         <v>9</v>
       </c>
       <c r="BK50" t="s">
@@ -2572,10 +2563,10 @@
       <c r="C51" t="s">
         <v>29</v>
       </c>
-      <c r="AX51" t="s">
-        <v>5</v>
-      </c>
-      <c r="AY51" t="s">
+      <c r="BA51" t="s">
+        <v>5</v>
+      </c>
+      <c r="BB51" t="s">
         <v>9</v>
       </c>
       <c r="BL51" t="s">
@@ -2604,10 +2595,10 @@
       <c r="C52" t="s">
         <v>30</v>
       </c>
-      <c r="AX52" t="s">
-        <v>5</v>
-      </c>
-      <c r="AY52" t="s">
+      <c r="BA52" t="s">
+        <v>5</v>
+      </c>
+      <c r="BB52" t="s">
         <v>9</v>
       </c>
       <c r="BL52" t="s">
@@ -2630,10 +2621,10 @@
       <c r="C53" t="s">
         <v>31</v>
       </c>
-      <c r="AY53" t="s">
-        <v>5</v>
-      </c>
-      <c r="AZ53" t="s">
+      <c r="BB53" t="s">
+        <v>5</v>
+      </c>
+      <c r="BC53" t="s">
         <v>9</v>
       </c>
       <c r="BL53" t="s">
@@ -2659,10 +2650,10 @@
       <c r="C54" t="s">
         <v>32</v>
       </c>
-      <c r="AY54" t="s">
-        <v>5</v>
-      </c>
-      <c r="AZ54" t="s">
+      <c r="BB54" t="s">
+        <v>5</v>
+      </c>
+      <c r="BC54" t="s">
         <v>9</v>
       </c>
       <c r="BM54" t="s">
@@ -2697,10 +2688,10 @@
       <c r="C55" t="s">
         <v>27</v>
       </c>
-      <c r="AZ55" t="s">
-        <v>5</v>
-      </c>
-      <c r="BA55" t="s">
+      <c r="BC55" t="s">
+        <v>5</v>
+      </c>
+      <c r="BD55" t="s">
         <v>9</v>
       </c>
       <c r="BQ55" t="s">
@@ -2732,10 +2723,10 @@
       <c r="C56" t="s">
         <v>28</v>
       </c>
-      <c r="AZ56" t="s">
-        <v>5</v>
-      </c>
-      <c r="BA56" t="s">
+      <c r="BC56" t="s">
+        <v>5</v>
+      </c>
+      <c r="BD56" t="s">
         <v>9</v>
       </c>
       <c r="BT56" t="s">
@@ -2770,10 +2761,10 @@
       <c r="C57" t="s">
         <v>29</v>
       </c>
-      <c r="AZ57" t="s">
-        <v>5</v>
-      </c>
       <c r="BC57" t="s">
+        <v>5</v>
+      </c>
+      <c r="BD57" t="s">
         <v>9</v>
       </c>
       <c r="BU57" t="s">
@@ -2802,10 +2793,10 @@
       <c r="C58" t="s">
         <v>30</v>
       </c>
-      <c r="AZ58" t="s">
-        <v>5</v>
-      </c>
       <c r="BC58" t="s">
+        <v>5</v>
+      </c>
+      <c r="BD58" t="s">
         <v>9</v>
       </c>
       <c r="BU58" t="s">
@@ -2828,10 +2819,10 @@
       <c r="C59" t="s">
         <v>31</v>
       </c>
-      <c r="BA59" t="s">
-        <v>5</v>
-      </c>
-      <c r="BC59" t="s">
+      <c r="BD59" t="s">
+        <v>5</v>
+      </c>
+      <c r="BE59" t="s">
         <v>9</v>
       </c>
       <c r="BU59" t="s">
@@ -2857,10 +2848,10 @@
       <c r="C60" t="s">
         <v>32</v>
       </c>
-      <c r="BA60" t="s">
-        <v>5</v>
-      </c>
-      <c r="BC60" t="s">
+      <c r="BD60" t="s">
+        <v>5</v>
+      </c>
+      <c r="BE60" t="s">
         <v>9</v>
       </c>
       <c r="BV60" t="s">
@@ -2895,10 +2886,10 @@
       <c r="C61" t="s">
         <v>27</v>
       </c>
-      <c r="BC61" t="s">
-        <v>5</v>
-      </c>
-      <c r="BD61" t="s">
+      <c r="BE61" t="s">
+        <v>5</v>
+      </c>
+      <c r="BF61" t="s">
         <v>9</v>
       </c>
       <c r="BZ61" t="s">
@@ -2930,7 +2921,7 @@
       <c r="C62" t="s">
         <v>28</v>
       </c>
-      <c r="BC62" t="s">
+      <c r="BE62" t="s">
         <v>5</v>
       </c>
       <c r="BG62" t="s">
@@ -2968,7 +2959,7 @@
       <c r="C63" t="s">
         <v>29</v>
       </c>
-      <c r="BC63" t="s">
+      <c r="BE63" t="s">
         <v>5</v>
       </c>
       <c r="BK63" t="s">
@@ -3000,7 +2991,7 @@
       <c r="C64" t="s">
         <v>30</v>
       </c>
-      <c r="BC64" t="s">
+      <c r="BE64" t="s">
         <v>5</v>
       </c>
       <c r="BK64" t="s">
@@ -3026,7 +3017,7 @@
       <c r="C65" t="s">
         <v>31</v>
       </c>
-      <c r="BD65" t="s">
+      <c r="BF65" t="s">
         <v>5</v>
       </c>
       <c r="BK65" t="s">
@@ -4170,6 +4161,9 @@
       <c r="DY100" t="s">
         <v>5</v>
       </c>
+      <c r="DZ100" t="s">
+        <v>9</v>
+      </c>
       <c r="EB100" t="s">
         <v>14</v>
       </c>
@@ -4190,22 +4184,16 @@
       <c r="C101" t="s">
         <v>39</v>
       </c>
-      <c r="DZ101" t="s">
-        <v>5</v>
-      </c>
-      <c r="EA101" t="s">
-        <v>9</v>
-      </c>
-      <c r="EB101" t="s">
-        <v>33</v>
-      </c>
       <c r="EC101" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="ED101" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="EE101" t="s">
+        <v>14</v>
+      </c>
+      <c r="EF101" t="s">
         <v>21</v>
       </c>
       <c r="EG101" t="s">
@@ -4222,14 +4210,11 @@
       <c r="C102" t="s">
         <v>40</v>
       </c>
-      <c r="DZ102" t="s">
-        <v>5</v>
-      </c>
-      <c r="EA102" t="s">
-        <v>9</v>
+      <c r="EC102" t="s">
+        <v>5</v>
       </c>
       <c r="ED102" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="EE102" t="s">
         <v>33</v>
@@ -4254,10 +4239,10 @@
       <c r="C103" t="s">
         <v>41</v>
       </c>
-      <c r="DZ103" t="s">
-        <v>5</v>
-      </c>
-      <c r="EA103" t="s">
+      <c r="EC103" t="s">
+        <v>5</v>
+      </c>
+      <c r="ED103" t="s">
         <v>9</v>
       </c>
       <c r="EG103" t="s">
@@ -4280,10 +4265,10 @@
       <c r="C104" t="s">
         <v>42</v>
       </c>
-      <c r="DZ104" t="s">
-        <v>5</v>
-      </c>
-      <c r="EA104" t="s">
+      <c r="EC104" t="s">
+        <v>5</v>
+      </c>
+      <c r="ED104" t="s">
         <v>9</v>
       </c>
       <c r="EG104" t="s">
@@ -4309,10 +4294,10 @@
       <c r="C105" t="s">
         <v>43</v>
       </c>
-      <c r="EA105" t="s">
-        <v>5</v>
-      </c>
-      <c r="EB105" t="s">
+      <c r="ED105" t="s">
+        <v>5</v>
+      </c>
+      <c r="EE105" t="s">
         <v>9</v>
       </c>
       <c r="EH105" t="s">
@@ -4338,10 +4323,10 @@
       <c r="C106" t="s">
         <v>44</v>
       </c>
-      <c r="EA106" t="s">
-        <v>5</v>
-      </c>
-      <c r="EB106" t="s">
+      <c r="ED106" t="s">
+        <v>5</v>
+      </c>
+      <c r="EE106" t="s">
         <v>9</v>
       </c>
       <c r="EI106" t="s">
@@ -4367,10 +4352,10 @@
       <c r="C107" t="s">
         <v>45</v>
       </c>
-      <c r="EA107" t="s">
-        <v>5</v>
-      </c>
-      <c r="EB107" t="s">
+      <c r="ED107" t="s">
+        <v>5</v>
+      </c>
+      <c r="EE107" t="s">
         <v>9</v>
       </c>
       <c r="EJ107" t="s">
@@ -4396,10 +4381,10 @@
       <c r="C108" t="s">
         <v>46</v>
       </c>
-      <c r="EA108" t="s">
-        <v>5</v>
-      </c>
-      <c r="EB108" t="s">
+      <c r="ED108" t="s">
+        <v>5</v>
+      </c>
+      <c r="EE108" t="s">
         <v>9</v>
       </c>
       <c r="EK108" t="s">
@@ -4425,10 +4410,10 @@
       <c r="C109" t="s">
         <v>47</v>
       </c>
-      <c r="EB109" t="s">
-        <v>5</v>
-      </c>
-      <c r="EC109" t="s">
+      <c r="EE109" t="s">
+        <v>5</v>
+      </c>
+      <c r="EF109" t="s">
         <v>9</v>
       </c>
       <c r="EL109" t="s">
